--- a/data/trans_dic/P25C$otrosprofesionales_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25C$otrosprofesionales_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, al menos, acupuntura u homeparía</t>
+          <t>Población cuyo método para dejar de fumar fue, al menos, acupuntura u homeparía (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 8,95</t>
+          <t>1,21; 10,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,0</t>
+          <t>0,6; 3,88</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 7,3</t>
+          <t>0,29; 7,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,79</t>
+          <t>0,11; 2,8</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,78</t>
+          <t>0,39; 3,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,87</t>
+          <t>0,68; 5,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,58</t>
+          <t>0,72; 3,39</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,31</t>
+          <t>0,0; 4,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,86</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,09</t>
+          <t>0,11; 1,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,3</t>
+          <t>0,99; 3,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,46</t>
+          <t>0,37; 1,52</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, al menos, acupuntura u homeparía</t>
+          <t>Población cuyo método para dejar de fumar fue, al menos, acupuntura u homeparía (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2737</t>
+          <t>0; 2957</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>661; 5821</t>
+          <t>790; 6771</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1142; 7537</t>
+          <t>1122; 7315</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1529</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>159; 4141</t>
+          <t>162; 4442</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>163; 4184</t>
+          <t>160; 4202</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4813</t>
+          <t>0; 4759</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1156</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4068</t>
+          <t>0; 5468</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>867; 7155</t>
+          <t>730; 7554</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>531; 4634</t>
+          <t>541; 4620</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1724; 9603</t>
+          <t>1929; 9093</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1508</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3019</t>
+          <t>0; 3126</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3294</t>
+          <t>0; 3122</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1843</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1169</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1264</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>952; 9152</t>
+          <t>946; 9559</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3221; 10897</t>
+          <t>3282; 10731</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4538; 17109</t>
+          <t>4358; 17782</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$otrosprofesionales_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25C$otrosprofesionales_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 10,41</t>
+          <t>1,01; 8,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,88</t>
+          <t>0,6; 3,87</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 7,83</t>
+          <t>0,98; 8,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,8</t>
+          <t>0,37; 3,49</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 3,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 3,04</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,99</t>
+          <t>0,46; 4,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,85</t>
+          <t>0,65; 6,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,39</t>
+          <t>0,81; 3,96</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -777,19 +777,19 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,46</t>
+          <t>0,0; 4,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,14</t>
+          <t>0,28; 1,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,25</t>
+          <t>0,95; 3,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,52</t>
+          <t>0,7; 1,89</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>691</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3273</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2957</t>
+          <t>0; 3562</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>790; 6771</t>
+          <t>702; 6086</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1122; 7315</t>
+          <t>1190; 7748</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>2040</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>162; 4442</t>
+          <t>613; 5453</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>160; 4202</t>
+          <t>603; 5770</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>669</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>669</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4759</t>
+          <t>0; 3469</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5468</t>
+          <t>0; 3885</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>5367</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>730; 7554</t>
+          <t>966; 9206</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>541; 4620</t>
+          <t>553; 5265</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1929; 9093</t>
+          <t>2393; 11719</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>667</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>667</t>
         </is>
       </c>
     </row>
@@ -1329,19 +1329,19 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3126</t>
+          <t>0; 3399</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3122</t>
+          <t>0; 3235</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>12016</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>946; 9559</t>
+          <t>1843; 10739</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3282; 10731</t>
+          <t>3395; 11868</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4358; 17782</t>
+          <t>7042; 19015</t>
         </is>
       </c>
     </row>
